--- a/patterns/jss-results.xlsx
+++ b/patterns/jss-results.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126B841E-ECEB-F54E-BC7D-D0F3E2DDAD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC4FBEE-6AFC-0149-B037-58BFB18D983B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="200" yWindow="1200" windowWidth="23540" windowHeight="14000" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="32460" yWindow="3320" windowWidth="26180" windowHeight="15240" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO" sheetId="1" r:id="rId1"/>
+    <sheet name="CQRS" sheetId="2" r:id="rId2"/>
+    <sheet name="ACL" sheetId="3" r:id="rId3"/>
+    <sheet name="GA" sheetId="4" r:id="rId4"/>
+    <sheet name="PAF" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="results_go" localSheetId="0">GO!$A$1:$L$34</definedName>
+    <definedName name="results_go" localSheetId="0">GO!$A$1:$L$28</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -62,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="19">
   <si>
     <t>method</t>
   </si>
@@ -116,6 +120,9 @@
   </si>
   <si>
     <t>cart</t>
+  </si>
+  <si>
+    <t>PAF</t>
   </si>
 </sst>
 </file>
@@ -396,8 +403,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -438,6 +446,7 @@
     <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E96F0A-AEE0-C546-9A77-15D1887CC59C}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -847,1030 +856,964 @@
     <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="17">
+      <c r="C2" s="11"/>
+      <c r="D2" s="18">
         <v>1</v>
       </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="21"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="21"/>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="1">
+        <f>SUM(D2:I2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="9">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="18">
+      <c r="C3" s="12"/>
+      <c r="D3" s="10">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0</v>
+      </c>
+      <c r="F3" s="19">
         <v>0.7</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="9">
-        <v>0</v>
-      </c>
-      <c r="I3" s="18">
+      <c r="G3" s="23"/>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="19">
         <v>0.3</v>
       </c>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="23"/>
-    </row>
-    <row r="4" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="1">
+        <f t="shared" ref="M3:M28" si="0">SUM(D3:I3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="19">
+      <c r="C4" s="13"/>
+      <c r="D4" s="20">
         <v>0.11111111111111099</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="20">
         <v>0.77777777777777701</v>
       </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="24"/>
-      <c r="H4" s="19">
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="20">
         <v>0.11111111111111099</v>
       </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="25"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999889</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <v>1</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="21"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="21"/>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="27">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0</v>
-      </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="9">
-        <v>0</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
-      </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="23"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="D6" s="28">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="23"/>
+      <c r="H6" s="10">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10">
+        <v>0</v>
+      </c>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="27">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0</v>
-      </c>
-      <c r="F7" s="9">
-        <v>0</v>
-      </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="9">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="23"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="D7" s="28">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+      <c r="G7" s="23"/>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="27">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9">
-        <v>0</v>
-      </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="9">
-        <v>0</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="23"/>
-    </row>
-    <row r="9" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="D8" s="28">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0</v>
+      </c>
+      <c r="G8" s="23"/>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0</v>
+      </c>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="28">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="4">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="25"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+      <c r="D9" s="29">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="25"/>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="29">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="21"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
+      <c r="D10" s="30">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="21"/>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="27">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9">
-        <v>0</v>
-      </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="9">
-        <v>0</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0</v>
-      </c>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="23"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+      <c r="D11" s="28">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0</v>
+      </c>
+      <c r="G11" s="23"/>
+      <c r="H11" s="10">
+        <v>0</v>
+      </c>
+      <c r="I11" s="10">
+        <v>0</v>
+      </c>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="27">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0</v>
-      </c>
-      <c r="F12" s="30">
+      <c r="D12" s="28">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="31">
         <v>0.875</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="9">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18">
+      <c r="G12" s="23"/>
+      <c r="H12" s="10">
+        <v>0</v>
+      </c>
+      <c r="I12" s="19">
         <v>0.125</v>
       </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="23"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="27">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0</v>
-      </c>
-      <c r="F13" s="9">
-        <v>0</v>
-      </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="9">
-        <v>0</v>
-      </c>
-      <c r="I13" s="9">
-        <v>0</v>
-      </c>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="23"/>
-    </row>
-    <row r="14" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="D13" s="28">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0</v>
+      </c>
+      <c r="G13" s="23"/>
+      <c r="H13" s="10">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10">
+        <v>0</v>
+      </c>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="28">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="D14" s="29">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
         <v>0.7</v>
       </c>
-      <c r="G14" s="24"/>
-      <c r="H14" s="4">
-        <v>0</v>
-      </c>
-      <c r="I14" s="31">
+      <c r="G14" s="25"/>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="32">
         <v>0.3</v>
       </c>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="25"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="32">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0</v>
-      </c>
-      <c r="F15" s="9">
-        <v>0</v>
-      </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="9">
-        <v>0</v>
-      </c>
-      <c r="I15" s="9">
-        <v>0</v>
-      </c>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="23"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
+      <c r="D15" s="33">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0</v>
+      </c>
+      <c r="G15" s="23"/>
+      <c r="H15" s="10">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10">
+        <v>0</v>
+      </c>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="19">
         <v>0.14285714285714199</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>0.85714285714285698</v>
       </c>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="9">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0</v>
-      </c>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="23"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="23"/>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
+        <v>0</v>
+      </c>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.999999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="9">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0</v>
-      </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="9">
-        <v>0</v>
-      </c>
-      <c r="I17" s="9">
-        <v>0</v>
-      </c>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="23"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+      <c r="D17" s="10">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0</v>
+      </c>
+      <c r="G17" s="23"/>
+      <c r="H17" s="10">
+        <v>0</v>
+      </c>
+      <c r="I17" s="10">
+        <v>0</v>
+      </c>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="18">
+      <c r="D18" s="10">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19">
         <v>0.66666666666666596</v>
       </c>
-      <c r="F18" s="9">
-        <v>0</v>
-      </c>
-      <c r="G18" s="22"/>
-      <c r="H18" s="30">
+      <c r="F18" s="10">
+        <v>0</v>
+      </c>
+      <c r="G18" s="23"/>
+      <c r="H18" s="31">
         <v>0.33333333333333298</v>
       </c>
-      <c r="I18" s="9">
-        <v>0</v>
-      </c>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="23"/>
-    </row>
-    <row r="19" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="I18" s="10">
+        <v>0</v>
+      </c>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999889</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4">
-        <v>0</v>
-      </c>
-      <c r="G19" s="24"/>
-      <c r="H19" s="4">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4">
-        <v>0</v>
-      </c>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="25"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="25"/>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <v>1</v>
       </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="2">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="21"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="27">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9">
-        <v>0</v>
-      </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="9">
-        <v>0</v>
-      </c>
-      <c r="I21" s="9">
-        <v>0</v>
-      </c>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="23"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
+      <c r="D21" s="28">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0</v>
+      </c>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="10">
+        <v>0</v>
+      </c>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="27">
+      <c r="C22" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="28">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="30">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="28">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0</v>
+      </c>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="10">
+        <v>0</v>
+      </c>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="29">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="5">
+        <v>0</v>
+      </c>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="33">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0</v>
+      </c>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="10">
+        <v>0</v>
+      </c>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0</v>
+      </c>
+      <c r="E27" s="31">
         <v>1</v>
       </c>
-      <c r="E22" s="9">
-        <v>0</v>
-      </c>
-      <c r="F22" s="9">
-        <v>0</v>
-      </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="9">
-        <v>0</v>
-      </c>
-      <c r="I22" s="9">
-        <v>0</v>
-      </c>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="23"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="10">
+        <v>0</v>
+      </c>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="15" t="s">
+      <c r="B28" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="27">
-        <v>0</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9">
-        <v>0</v>
-      </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="9">
-        <v>0</v>
-      </c>
-      <c r="I23" s="9">
-        <v>0</v>
-      </c>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="23"/>
-    </row>
-    <row r="24" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="28">
+      <c r="D28" s="5">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="1">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4">
-        <v>0</v>
-      </c>
-      <c r="G24" s="24"/>
-      <c r="H24" s="4">
-        <v>0</v>
-      </c>
-      <c r="I24" s="4">
-        <v>0</v>
-      </c>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="25"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="29">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="21"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="27">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0</v>
-      </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="9">
-        <v>0</v>
-      </c>
-      <c r="I26" s="9">
-        <v>0</v>
-      </c>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="23"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="27">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9">
-        <v>0</v>
-      </c>
-      <c r="F27" s="30">
-        <v>1</v>
-      </c>
-      <c r="G27" s="22"/>
-      <c r="H27" s="9">
-        <v>0</v>
-      </c>
-      <c r="I27" s="9">
-        <v>0</v>
-      </c>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="23"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="27">
-        <v>0</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0</v>
-      </c>
-      <c r="F28" s="9">
-        <v>0</v>
-      </c>
-      <c r="G28" s="22"/>
-      <c r="H28" s="9">
-        <v>0</v>
-      </c>
-      <c r="I28" s="9">
-        <v>0</v>
-      </c>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="23"/>
-    </row>
-    <row r="29" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="28">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4">
-        <v>0</v>
-      </c>
-      <c r="G29" s="24"/>
-      <c r="H29" s="4">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4">
-        <v>0</v>
-      </c>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="25"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="32">
-        <v>0</v>
-      </c>
-      <c r="E30" s="9">
-        <v>0</v>
-      </c>
-      <c r="F30" s="9">
-        <v>0</v>
-      </c>
-      <c r="G30" s="22"/>
-      <c r="H30" s="9">
-        <v>0</v>
-      </c>
-      <c r="I30" s="9">
-        <v>0</v>
-      </c>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="23"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="9">
-        <v>0</v>
-      </c>
-      <c r="E31" s="32">
-        <v>0</v>
-      </c>
-      <c r="F31" s="9">
-        <v>0</v>
-      </c>
-      <c r="G31" s="22"/>
-      <c r="H31" s="9">
-        <v>0</v>
-      </c>
-      <c r="I31" s="9">
-        <v>0</v>
-      </c>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="23"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="18">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="E32" s="18">
-        <v>0.66666666666666596</v>
-      </c>
-      <c r="F32" s="9">
-        <v>0</v>
-      </c>
-      <c r="G32" s="22"/>
-      <c r="H32" s="9">
-        <v>0</v>
-      </c>
-      <c r="I32" s="9">
-        <v>0</v>
-      </c>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="23"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="9">
-        <v>0</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0</v>
-      </c>
-      <c r="F33" s="9">
-        <v>0</v>
-      </c>
-      <c r="G33" s="22"/>
-      <c r="H33" s="32">
-        <v>0</v>
-      </c>
-      <c r="I33" s="9">
-        <v>0</v>
-      </c>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="23"/>
-    </row>
-    <row r="34" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="19">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4">
-        <v>0</v>
-      </c>
-      <c r="G34" s="24"/>
-      <c r="H34" s="4">
-        <v>0</v>
-      </c>
-      <c r="I34" s="4">
-        <v>0</v>
-      </c>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF50480-301C-0843-A08D-1FF82088E86E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F99F23E7-3B71-1E4B-89E7-8EECD61E4DE0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26299AB8-0881-F840-8E86-BEA796FBE472}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DA0CDA-DFE2-7A44-A59F-25A5C13DA4B5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/patterns/jss-results.xlsx
+++ b/patterns/jss-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC4FBEE-6AFC-0149-B037-58BFB18D983B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80692318-4903-DB4F-A8B9-46C0B1F39992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32460" yWindow="3320" windowWidth="26180" windowHeight="15240" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="2360" yWindow="1060" windowWidth="22180" windowHeight="14600" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,11 @@
     <sheet name="PAF" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="results_acl" localSheetId="2">ACL!$A$1:$L$5</definedName>
+    <definedName name="results_cqrs" localSheetId="1">CQRS!$A$1:$L$11</definedName>
+    <definedName name="results_ga" localSheetId="3">GA!$A$1:$L$10</definedName>
     <definedName name="results_go" localSheetId="0">GO!$A$1:$L$28</definedName>
+    <definedName name="results_paf" localSheetId="4">PAF!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -44,8 +48,80 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{E1C4C421-FD73-1943-A59D-0B4297A00006}" name="results-go" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="1" xr16:uid="{BF63BA1D-9B02-F54D-AE9B-598A4ECE2858}" name="results-acl" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/Anti_Corruption_Layer/results-acl.csv" decimal="," thousands="." comma="1">
+      <textFields count="12">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="2" xr16:uid="{655D14C4-C9C8-8A41-AF98-37321038F32B}" name="results-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/CQRS/results-cqrs.csv" decimal="," thousands="." comma="1">
+      <textFields count="12">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="3" xr16:uid="{50E58DC9-1708-4C4A-85B4-9AD199D6C9CB}" name="results-ga" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/Gateway_Aggregation/results-ga.csv" decimal="," thousands="." comma="1">
+      <textFields count="12">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="4" xr16:uid="{E1C4C421-FD73-1943-A59D-0B4297A00006}" name="results-go" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/Gateway_Offloading/results-go.csv" decimal="," thousands="." comma="1">
+      <textFields count="12">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="5" xr16:uid="{286C5DEF-A7D6-4543-AF19-2EDD11C216CF}" name="results-paf" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/Pipes_and_Filters/results-paf.csv" decimal="," thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -66,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="24">
   <si>
     <t>method</t>
   </si>
@@ -122,14 +198,29 @@
     <t>cart</t>
   </si>
   <si>
-    <t>PAF</t>
+    <t>hardware</t>
+  </si>
+  <si>
+    <t>software</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>joint1</t>
+  </si>
+  <si>
+    <t>joint2</t>
+  </si>
+  <si>
+    <t>separated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -139,6 +230,12 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -177,7 +274,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -399,17 +496,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -421,6 +570,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
@@ -447,6 +597,47 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,8 +710,244 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64160646-2376-EABE-E21A-9A60BF033EA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11404600" y="228600"/>
+          <a:ext cx="7315200" cy="6388100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D1B6955-605C-25BE-8B67-A29E71F3334C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11176000" y="317500"/>
+          <a:ext cx="7315200" cy="6388100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>774700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C5CD18B-A380-DBD0-3659-EDBBDEAEAD28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12090400" y="444500"/>
+          <a:ext cx="7315200" cy="6388100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B2C3A28-DC44-E2B6-E414-979B8237D303}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11747500" y="584200"/>
+          <a:ext cx="7315200" cy="6388100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results-go" connectionId="1" xr16:uid="{D2487251-32FB-3B40-8C28-889D9D04D2A4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results-go" connectionId="4" xr16:uid="{D2487251-32FB-3B40-8C28-889D9D04D2A4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results-cqrs" connectionId="2" xr16:uid="{1E585FE2-AC80-D34B-89C8-2DBB7D3F48FA}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results-acl" connectionId="1" xr16:uid="{C0147E74-3E8B-E843-9581-45696DB169C9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results-ga" connectionId="3" xr16:uid="{9D41BD05-56BC-2940-8FB0-E5C62E1B2F5F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results-paf" connectionId="5" xr16:uid="{B25F2EF1-0743-0544-BEFA-518744ABEBF3}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -857,40 +1284,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="14" t="s">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
@@ -898,11 +1325,11 @@
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="18">
+      <c r="C2" s="14"/>
+      <c r="D2" s="21">
         <v>1</v>
       </c>
       <c r="E2" s="3">
@@ -911,80 +1338,80 @@
       <c r="F2" s="3">
         <v>0</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="24"/>
       <c r="H2" s="3">
         <v>0</v>
       </c>
       <c r="I2" s="3">
         <v>0</v>
       </c>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="22"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="25"/>
       <c r="M2" s="1">
-        <f>SUM(D2:I2)</f>
+        <f>SUM(D2:L2)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="10">
-        <v>0</v>
-      </c>
-      <c r="E3" s="10">
-        <v>0</v>
-      </c>
-      <c r="F3" s="19">
+      <c r="C3" s="15"/>
+      <c r="D3" s="12">
+        <v>0</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0</v>
+      </c>
+      <c r="F3" s="22">
         <v>0.7</v>
       </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="19">
+      <c r="G3" s="26"/>
+      <c r="H3" s="12">
+        <v>0</v>
+      </c>
+      <c r="I3" s="22">
         <v>0.3</v>
       </c>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="24"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="27"/>
       <c r="M3" s="1">
-        <f t="shared" ref="M3:M28" si="0">SUM(D3:I3)</f>
+        <f t="shared" ref="M3:M28" si="0">SUM(D3:L3)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="20">
+      <c r="C4" s="16"/>
+      <c r="D4" s="23">
         <v>0.11111111111111099</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="23">
         <v>0.77777777777777701</v>
       </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="20">
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="23">
         <v>0.11111111111111099</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="26"/>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="29"/>
       <c r="M4" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -994,13 +1421,13 @@
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="30">
         <v>1</v>
       </c>
       <c r="E5" s="3">
@@ -1009,168 +1436,168 @@
       <c r="F5" s="3">
         <v>0</v>
       </c>
-      <c r="G5" s="21"/>
+      <c r="G5" s="24"/>
       <c r="H5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3">
         <v>0</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="22"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="28">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="10">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10">
-        <v>0</v>
-      </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="24"/>
+      <c r="D6" s="31">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0</v>
+      </c>
+      <c r="G6" s="26"/>
+      <c r="H6" s="12">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="28">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0</v>
-      </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="10">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="24"/>
+      <c r="D7" s="31">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0</v>
+      </c>
+      <c r="G7" s="26"/>
+      <c r="H7" s="12">
+        <v>0</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0</v>
+      </c>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="28">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0</v>
-      </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="10">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10">
-        <v>0</v>
-      </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="24"/>
+      <c r="D8" s="31">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0</v>
+      </c>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="29">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="26"/>
+      <c r="D9" s="32">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28"/>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="29"/>
       <c r="M9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="33">
         <v>0</v>
       </c>
       <c r="E10" s="3">
@@ -1179,322 +1606,322 @@
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="21"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="3">
         <v>0</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="22"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="25"/>
       <c r="M10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="28">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="10">
-        <v>0</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0</v>
-      </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="24"/>
+      <c r="D11" s="31">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0</v>
+      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="27"/>
       <c r="M11" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="28">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10">
-        <v>0</v>
-      </c>
-      <c r="F12" s="31">
+      <c r="D12" s="31">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="34">
         <v>0.875</v>
       </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="10">
-        <v>0</v>
-      </c>
-      <c r="I12" s="19">
+      <c r="G12" s="26"/>
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="22">
         <v>0.125</v>
       </c>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="24"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="27"/>
       <c r="M12" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="28">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10">
-        <v>0</v>
-      </c>
-      <c r="F13" s="10">
-        <v>0</v>
-      </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="10">
-        <v>0</v>
-      </c>
-      <c r="I13" s="10">
-        <v>0</v>
-      </c>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="24"/>
+      <c r="D13" s="31">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="12">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0</v>
+      </c>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="27"/>
       <c r="M13" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="29">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0</v>
-      </c>
-      <c r="F14" s="5">
+      <c r="D14" s="32">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
         <v>0.7</v>
       </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="5">
-        <v>0</v>
-      </c>
-      <c r="I14" s="32">
+      <c r="G14" s="28"/>
+      <c r="H14" s="6">
+        <v>0</v>
+      </c>
+      <c r="I14" s="35">
         <v>0.3</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="26"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="29"/>
       <c r="M14" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="33">
-        <v>0</v>
-      </c>
-      <c r="E15" s="10">
-        <v>0</v>
-      </c>
-      <c r="F15" s="10">
-        <v>0</v>
-      </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="10">
-        <v>0</v>
-      </c>
-      <c r="I15" s="10">
-        <v>0</v>
-      </c>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="24"/>
+      <c r="D15" s="36">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="26"/>
+      <c r="H15" s="12">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12">
+        <v>0</v>
+      </c>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="27"/>
       <c r="M15" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="22">
         <v>0.14285714285714199</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="34">
         <v>0.85714285714285698</v>
       </c>
-      <c r="F16" s="10">
-        <v>0</v>
-      </c>
-      <c r="G16" s="23"/>
-      <c r="H16" s="10">
-        <v>0</v>
-      </c>
-      <c r="I16" s="10">
-        <v>0</v>
-      </c>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="24"/>
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="26"/>
+      <c r="H16" s="12">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0</v>
+      </c>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="27"/>
       <c r="M16" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="10">
-        <v>0</v>
-      </c>
-      <c r="E17" s="10">
-        <v>0</v>
-      </c>
-      <c r="F17" s="10">
-        <v>0</v>
-      </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="10">
-        <v>0</v>
-      </c>
-      <c r="I17" s="10">
-        <v>0</v>
-      </c>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="24"/>
+      <c r="D17" s="12">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
+      <c r="G17" s="26"/>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12">
+        <v>0</v>
+      </c>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="27"/>
       <c r="M17" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="10">
-        <v>0</v>
-      </c>
-      <c r="E18" s="19">
+      <c r="D18" s="12">
+        <v>0</v>
+      </c>
+      <c r="E18" s="22">
         <v>0.66666666666666596</v>
       </c>
-      <c r="F18" s="10">
-        <v>0</v>
-      </c>
-      <c r="G18" s="23"/>
-      <c r="H18" s="31">
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="26"/>
+      <c r="H18" s="34">
         <v>0.33333333333333298</v>
       </c>
-      <c r="I18" s="10">
-        <v>0</v>
-      </c>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="24"/>
+      <c r="I18" s="12">
+        <v>0</v>
+      </c>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="27"/>
       <c r="M18" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="5">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="5">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0</v>
-      </c>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="26"/>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" s="28"/>
+      <c r="H19" s="6">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6">
+        <v>0</v>
+      </c>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="29"/>
       <c r="M19" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1504,267 +1931,267 @@
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="30">
         <v>1</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="22"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="25"/>
       <c r="M20" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="28">
-        <v>0</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0</v>
-      </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="10">
-        <v>0</v>
-      </c>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="24"/>
+      <c r="D21" s="31">
+        <v>0</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0</v>
+      </c>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="12">
+        <v>0</v>
+      </c>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="27"/>
       <c r="M21" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="28">
-        <v>0</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0</v>
-      </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="10">
-        <v>0</v>
-      </c>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="24"/>
+      <c r="D22" s="31">
+        <v>0</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="12">
+        <v>0</v>
+      </c>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="27"/>
       <c r="M22" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="33">
         <v>0</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
       </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
       <c r="H23" s="3">
         <v>0</v>
       </c>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="22"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="25"/>
       <c r="M23" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="28">
-        <v>0</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0</v>
-      </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="10">
-        <v>0</v>
-      </c>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="24"/>
+      <c r="D24" s="31">
+        <v>0</v>
+      </c>
+      <c r="E24" s="12">
+        <v>0</v>
+      </c>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="12">
+        <v>0</v>
+      </c>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="27"/>
       <c r="M24" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="29">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5">
-        <v>0</v>
-      </c>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="5">
-        <v>0</v>
-      </c>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="26"/>
+      <c r="D25" s="32">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="29"/>
       <c r="M25" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="33">
-        <v>0</v>
-      </c>
-      <c r="E26" s="10">
-        <v>0</v>
-      </c>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="10">
-        <v>0</v>
-      </c>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="24"/>
+      <c r="D26" s="36">
+        <v>0</v>
+      </c>
+      <c r="E26" s="12">
+        <v>0</v>
+      </c>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="12">
+        <v>0</v>
+      </c>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="27"/>
       <c r="M26" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="10">
-        <v>0</v>
-      </c>
-      <c r="E27" s="31">
-        <v>1</v>
-      </c>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="10">
-        <v>0</v>
-      </c>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="24"/>
+      <c r="D27" s="12">
+        <v>0</v>
+      </c>
+      <c r="E27" s="34">
+        <v>1</v>
+      </c>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="12">
+        <v>0</v>
+      </c>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="27"/>
       <c r="M27" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="5">
-        <v>0</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="D28" s="6">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
         <v>0.5</v>
       </c>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="34">
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="37">
         <v>0.5</v>
       </c>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="26"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="29"/>
       <c r="M28" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1778,42 +2205,1473 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF50480-301C-0843-A08D-1FF82088E86E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="49">
+        <v>0.28346456692913302</v>
+      </c>
+      <c r="E2" s="49">
+        <v>0.66929133858267698</v>
+      </c>
+      <c r="F2" s="49">
+        <v>2.3622047244094401E-2</v>
+      </c>
+      <c r="G2" s="49">
+        <v>0</v>
+      </c>
+      <c r="H2" s="49">
+        <v>7.8740157480314907E-3</v>
+      </c>
+      <c r="I2" s="49">
+        <v>1.5748031496062902E-2</v>
+      </c>
+      <c r="J2" s="49">
+        <v>0</v>
+      </c>
+      <c r="K2" s="49">
+        <v>0</v>
+      </c>
+      <c r="L2" s="50">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <f>SUM(D2:L2)</f>
+        <v>0.99999999999999878</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="44">
+        <v>0</v>
+      </c>
+      <c r="E3" s="44">
+        <v>0</v>
+      </c>
+      <c r="F3" s="44">
+        <v>1</v>
+      </c>
+      <c r="G3" s="44">
+        <v>0</v>
+      </c>
+      <c r="H3" s="44">
+        <v>0</v>
+      </c>
+      <c r="I3" s="44">
+        <v>0</v>
+      </c>
+      <c r="J3" s="44">
+        <v>0</v>
+      </c>
+      <c r="K3" s="44">
+        <v>0</v>
+      </c>
+      <c r="L3" s="45">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <f t="shared" ref="M3:M11" si="0">SUM(D3:L3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="49">
+        <v>0.6</v>
+      </c>
+      <c r="E4" s="49">
+        <v>0.4</v>
+      </c>
+      <c r="F4" s="49">
+        <v>0</v>
+      </c>
+      <c r="G4" s="64"/>
+      <c r="H4" s="49">
+        <v>0</v>
+      </c>
+      <c r="I4" s="49">
+        <v>0</v>
+      </c>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="42">
+        <v>0.31034482758620602</v>
+      </c>
+      <c r="E5" s="42">
+        <v>0.68965517241379304</v>
+      </c>
+      <c r="F5" s="42">
+        <v>0</v>
+      </c>
+      <c r="G5" s="65"/>
+      <c r="H5" s="42">
+        <v>0</v>
+      </c>
+      <c r="I5" s="42">
+        <v>0</v>
+      </c>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999911</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="42">
+        <v>0.30769230769230699</v>
+      </c>
+      <c r="E6" s="42">
+        <v>0.64102564102564097</v>
+      </c>
+      <c r="F6" s="42">
+        <v>2.5641025641025599E-2</v>
+      </c>
+      <c r="G6" s="65"/>
+      <c r="H6" s="42">
+        <v>8.5470085470085392E-3</v>
+      </c>
+      <c r="I6" s="42">
+        <v>1.7094017094016999E-2</v>
+      </c>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999911</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="44">
+        <v>0</v>
+      </c>
+      <c r="E7" s="44">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="F7" s="44">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G7" s="66"/>
+      <c r="H7" s="44">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="I7" s="44">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999689</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="42">
+        <v>0</v>
+      </c>
+      <c r="E8" s="42">
+        <v>0</v>
+      </c>
+      <c r="F8" s="42">
+        <v>1</v>
+      </c>
+      <c r="G8" s="65"/>
+      <c r="H8" s="42">
+        <v>0</v>
+      </c>
+      <c r="I8" s="42">
+        <v>0</v>
+      </c>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="42">
+        <v>0</v>
+      </c>
+      <c r="E9" s="42">
+        <v>0</v>
+      </c>
+      <c r="F9" s="42">
+        <v>1</v>
+      </c>
+      <c r="G9" s="65"/>
+      <c r="H9" s="42">
+        <v>0</v>
+      </c>
+      <c r="I9" s="42">
+        <v>0</v>
+      </c>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="42">
+        <v>0</v>
+      </c>
+      <c r="E10" s="42">
+        <v>0</v>
+      </c>
+      <c r="F10" s="42">
+        <v>1</v>
+      </c>
+      <c r="G10" s="65"/>
+      <c r="H10" s="42">
+        <v>0</v>
+      </c>
+      <c r="I10" s="42">
+        <v>0</v>
+      </c>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="44">
+        <v>0</v>
+      </c>
+      <c r="E11" s="44">
+        <v>0</v>
+      </c>
+      <c r="F11" s="44">
+        <v>1</v>
+      </c>
+      <c r="G11" s="66"/>
+      <c r="H11" s="44">
+        <v>0</v>
+      </c>
+      <c r="I11" s="44">
+        <v>0</v>
+      </c>
+      <c r="J11" s="66"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F99F23E7-3B71-1E4B-89E7-8EECD61E4DE0}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="56">
+        <v>0.48913043478260798</v>
+      </c>
+      <c r="E2" s="56">
+        <v>0.48913043478260798</v>
+      </c>
+      <c r="F2" s="56">
+        <v>2.1739130434782601E-2</v>
+      </c>
+      <c r="G2" s="56">
+        <v>0</v>
+      </c>
+      <c r="H2" s="56">
+        <v>0</v>
+      </c>
+      <c r="I2" s="56">
+        <v>0</v>
+      </c>
+      <c r="J2" s="56">
+        <v>0</v>
+      </c>
+      <c r="K2" s="56">
+        <v>0</v>
+      </c>
+      <c r="L2" s="57">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <f>SUM(D2:L2)</f>
+        <v>0.99999999999999856</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="1">
+        <f t="shared" ref="M3:M5" si="0">SUM(D3:L3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.17391304347826</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.80434782608695599</v>
+      </c>
+      <c r="F5" s="6">
+        <v>2.1739130434782601E-2</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999856</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26299AB8-0881-F840-8E86-BEA796FBE472}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="56">
+        <v>0.15625</v>
+      </c>
+      <c r="E2" s="56">
+        <v>0</v>
+      </c>
+      <c r="F2" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="56">
+        <v>9.375E-2</v>
+      </c>
+      <c r="H2" s="56">
+        <v>0</v>
+      </c>
+      <c r="I2" s="56">
+        <v>3.125E-2</v>
+      </c>
+      <c r="J2" s="56">
+        <v>0.4375</v>
+      </c>
+      <c r="K2" s="56">
+        <v>0</v>
+      </c>
+      <c r="L2" s="57">
+        <v>3.125E-2</v>
+      </c>
+      <c r="M2" s="1">
+        <f>SUM(D2:L2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.1875</v>
+      </c>
+      <c r="E3" s="24"/>
+      <c r="F3" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="K3" s="24"/>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <f t="shared" ref="M3:M10" si="0">SUM(D3:L3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="12">
+        <v>0.217391304347826</v>
+      </c>
+      <c r="E4" s="26"/>
+      <c r="F4" s="12">
+        <v>0.34782608695652101</v>
+      </c>
+      <c r="G4" s="12">
+        <v>4.3478260869565202E-2</v>
+      </c>
+      <c r="H4" s="26"/>
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0.39130434782608697</v>
+      </c>
+      <c r="K4" s="26"/>
+      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999911</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="12">
+        <v>0.17241379310344801</v>
+      </c>
+      <c r="E5" s="26"/>
+      <c r="F5" s="12">
+        <v>0.27586206896551702</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0.10344827586206801</v>
+      </c>
+      <c r="H5" s="26"/>
+      <c r="I5" s="12">
+        <v>3.4482758620689599E-2</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0.41379310344827502</v>
+      </c>
+      <c r="K5" s="26"/>
+      <c r="L5" s="13">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999767</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0.17241379310344801</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="12">
+        <v>0.27586206896551702</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.10344827586206801</v>
+      </c>
+      <c r="H6" s="26"/>
+      <c r="I6" s="12">
+        <v>3.4482758620689599E-2</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0.41379310344827502</v>
+      </c>
+      <c r="K6" s="26"/>
+      <c r="L6" s="13">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999767</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="12">
+        <v>0.20833333333333301</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="12">
+        <v>0.29166666666666602</v>
+      </c>
+      <c r="G7" s="12">
+        <v>8.3333333333333301E-2</v>
+      </c>
+      <c r="H7" s="26"/>
+      <c r="I7" s="12">
+        <v>4.1666666666666602E-2</v>
+      </c>
+      <c r="J7" s="12">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="K7" s="26"/>
+      <c r="L7" s="13">
+        <v>4.1666666666666602E-2</v>
+      </c>
+      <c r="M7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999856</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28"/>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="K8" s="28"/>
+      <c r="L8" s="7">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="M8" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999889</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.1875</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="H9" s="24"/>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="24"/>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="E10" s="28"/>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="28"/>
+      <c r="I10" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="K10" s="28"/>
+      <c r="L10" s="7">
+        <v>0.125</v>
+      </c>
+      <c r="M10" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DA0CDA-DFE2-7A44-A59F-25A5C13DA4B5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>18</v>
+    <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.60869565217391297</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0.34782608695652101</v>
+      </c>
+      <c r="L2" s="4">
+        <v>4.3478260869565202E-2</v>
+      </c>
+      <c r="M2" s="1">
+        <f>SUM(D2:L2)</f>
+        <v>0.99999999999999911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="12">
+        <v>9.5238095238095205E-2</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0</v>
+      </c>
+      <c r="H3" s="12">
+        <v>4.7619047619047603E-2</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0</v>
+      </c>
+      <c r="K3" s="12">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <f t="shared" ref="M3:M13" si="0">SUM(D3:L3)</f>
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="12">
+        <v>0</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0</v>
+      </c>
+      <c r="K4" s="12">
+        <v>5.5555555555555497E-2</v>
+      </c>
+      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999944</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="33">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="3">
+        <v>0.76470588235294101</v>
+      </c>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="3">
+        <v>0.23529411764705799</v>
+      </c>
+      <c r="L5" s="25"/>
+      <c r="M5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.999999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="31">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="12">
+        <v>0.18181818181818099</v>
+      </c>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="12">
+        <v>0.72727272727272696</v>
+      </c>
+      <c r="L6" s="27"/>
+      <c r="M6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.90909090909090795</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="31">
+        <v>0.125</v>
+      </c>
+      <c r="E7" s="12">
+        <v>0.875</v>
+      </c>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="12">
+        <v>0</v>
+      </c>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="12">
+        <v>0</v>
+      </c>
+      <c r="L7" s="27"/>
+      <c r="M7" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="12">
+        <v>0</v>
+      </c>
+      <c r="L8" s="27"/>
+      <c r="M8" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="31">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0.92857142857142805</v>
+      </c>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="12">
+        <v>7.1428571428571397E-2</v>
+      </c>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="12">
+        <v>0</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999944</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="32">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="L10" s="29"/>
+      <c r="M10" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="12">
+        <v>1</v>
+      </c>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999889</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/patterns/jss-results.xlsx
+++ b/patterns/jss-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80692318-4903-DB4F-A8B9-46C0B1F39992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AE7345-84C1-BF4B-894E-4831D8CC5754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2360" yWindow="1060" windowWidth="22180" windowHeight="14600" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="2360" yWindow="1060" windowWidth="22180" windowHeight="14600" activeTab="4" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO" sheetId="1" r:id="rId1"/>
@@ -274,7 +274,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -546,11 +546,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -608,26 +621,20 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -638,6 +645,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2299,38 +2319,38 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="44" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="47"/>
-      <c r="D3" s="44">
-        <v>0</v>
-      </c>
-      <c r="E3" s="44">
-        <v>0</v>
-      </c>
-      <c r="F3" s="44">
-        <v>1</v>
-      </c>
-      <c r="G3" s="44">
-        <v>0</v>
-      </c>
-      <c r="H3" s="44">
-        <v>0</v>
-      </c>
-      <c r="I3" s="44">
-        <v>0</v>
-      </c>
-      <c r="J3" s="44">
-        <v>0</v>
-      </c>
-      <c r="K3" s="44">
-        <v>0</v>
-      </c>
-      <c r="L3" s="45">
+      <c r="D3" s="42">
+        <v>0</v>
+      </c>
+      <c r="E3" s="42">
+        <v>0</v>
+      </c>
+      <c r="F3" s="42">
+        <v>1</v>
+      </c>
+      <c r="G3" s="42">
+        <v>0</v>
+      </c>
+      <c r="H3" s="42">
+        <v>0</v>
+      </c>
+      <c r="I3" s="42">
+        <v>0</v>
+      </c>
+      <c r="J3" s="42">
+        <v>0</v>
+      </c>
+      <c r="K3" s="42">
+        <v>0</v>
+      </c>
+      <c r="L3" s="43">
         <v>0</v>
       </c>
       <c r="M3" s="1">
@@ -2345,10 +2365,10 @@
       <c r="B4" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="49">
+      <c r="D4" s="75">
         <v>0.6</v>
       </c>
       <c r="E4" s="49">
@@ -2357,16 +2377,16 @@
       <c r="F4" s="49">
         <v>0</v>
       </c>
-      <c r="G4" s="64"/>
+      <c r="G4" s="58"/>
       <c r="H4" s="49">
         <v>0</v>
       </c>
       <c r="I4" s="49">
         <v>0</v>
       </c>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="67"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="61"/>
       <c r="M4" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2379,10 +2399,10 @@
       <c r="B5" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="76">
         <v>0.31034482758620602</v>
       </c>
       <c r="E5" s="42">
@@ -2391,16 +2411,16 @@
       <c r="F5" s="42">
         <v>0</v>
       </c>
-      <c r="G5" s="65"/>
+      <c r="G5" s="59"/>
       <c r="H5" s="42">
         <v>0</v>
       </c>
       <c r="I5" s="42">
         <v>0</v>
       </c>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="68"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="62"/>
       <c r="M5" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999911</v>
@@ -2413,10 +2433,10 @@
       <c r="B6" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="76">
         <v>0.30769230769230699</v>
       </c>
       <c r="E6" s="42">
@@ -2425,16 +2445,16 @@
       <c r="F6" s="42">
         <v>2.5641025641025599E-2</v>
       </c>
-      <c r="G6" s="65"/>
+      <c r="G6" s="59"/>
       <c r="H6" s="42">
         <v>8.5470085470085392E-3</v>
       </c>
       <c r="I6" s="42">
         <v>1.7094017094016999E-2</v>
       </c>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="68"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="62"/>
       <c r="M6" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999911</v>
@@ -2444,31 +2464,31 @@
       <c r="A7" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="44">
-        <v>0</v>
-      </c>
-      <c r="E7" s="44">
+      <c r="D7" s="79">
+        <v>0</v>
+      </c>
+      <c r="E7" s="45">
         <v>0.28571428571428498</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="45">
         <v>0.28571428571428498</v>
       </c>
-      <c r="G7" s="66"/>
-      <c r="H7" s="44">
+      <c r="G7" s="60"/>
+      <c r="H7" s="45">
         <v>0.14285714285714199</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="45">
         <v>0.28571428571428498</v>
       </c>
-      <c r="J7" s="66"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="69"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="63"/>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999689</v>
@@ -2481,28 +2501,28 @@
       <c r="B8" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="42">
-        <v>0</v>
-      </c>
-      <c r="E8" s="42">
+      <c r="D8" s="77">
+        <v>0</v>
+      </c>
+      <c r="E8" s="67">
         <v>0</v>
       </c>
       <c r="F8" s="42">
         <v>1</v>
       </c>
-      <c r="G8" s="65"/>
-      <c r="H8" s="42">
-        <v>0</v>
-      </c>
-      <c r="I8" s="42">
-        <v>0</v>
-      </c>
-      <c r="J8" s="65"/>
-      <c r="K8" s="65"/>
-      <c r="L8" s="68"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="67">
+        <v>0</v>
+      </c>
+      <c r="I8" s="67">
+        <v>0</v>
+      </c>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="62"/>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2515,28 +2535,28 @@
       <c r="B9" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="42">
-        <v>0</v>
-      </c>
-      <c r="E9" s="42">
+      <c r="D9" s="77">
+        <v>0</v>
+      </c>
+      <c r="E9" s="67">
         <v>0</v>
       </c>
       <c r="F9" s="42">
         <v>1</v>
       </c>
-      <c r="G9" s="65"/>
-      <c r="H9" s="42">
-        <v>0</v>
-      </c>
-      <c r="I9" s="42">
-        <v>0</v>
-      </c>
-      <c r="J9" s="65"/>
-      <c r="K9" s="65"/>
-      <c r="L9" s="68"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="67">
+        <v>0</v>
+      </c>
+      <c r="I9" s="67">
+        <v>0</v>
+      </c>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="62"/>
       <c r="M9" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2549,82 +2569,82 @@
       <c r="B10" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="42">
-        <v>0</v>
-      </c>
-      <c r="E10" s="42">
+      <c r="D10" s="77">
+        <v>0</v>
+      </c>
+      <c r="E10" s="67">
         <v>0</v>
       </c>
       <c r="F10" s="42">
         <v>1</v>
       </c>
-      <c r="G10" s="65"/>
-      <c r="H10" s="42">
-        <v>0</v>
-      </c>
-      <c r="I10" s="42">
-        <v>0</v>
-      </c>
-      <c r="J10" s="65"/>
-      <c r="K10" s="65"/>
-      <c r="L10" s="68"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="67">
+        <v>0</v>
+      </c>
+      <c r="I10" s="67">
+        <v>0</v>
+      </c>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="62"/>
       <c r="M10" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="44">
-        <v>0</v>
-      </c>
-      <c r="E11" s="44">
-        <v>0</v>
-      </c>
-      <c r="F11" s="44">
-        <v>1</v>
-      </c>
-      <c r="G11" s="66"/>
-      <c r="H11" s="44">
-        <v>0</v>
-      </c>
-      <c r="I11" s="44">
-        <v>0</v>
-      </c>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="69"/>
+      <c r="D11" s="78">
+        <v>0</v>
+      </c>
+      <c r="E11" s="68">
+        <v>0</v>
+      </c>
+      <c r="F11" s="45">
+        <v>1</v>
+      </c>
+      <c r="G11" s="60"/>
+      <c r="H11" s="68">
+        <v>0</v>
+      </c>
+      <c r="I11" s="68">
+        <v>0</v>
+      </c>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="63"/>
       <c r="M11" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="60" t="s">
+      <c r="A12" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="62"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="74"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2689,38 +2709,38 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="56">
+      <c r="C2" s="54"/>
+      <c r="D2" s="52">
         <v>0.48913043478260798</v>
       </c>
-      <c r="E2" s="56">
+      <c r="E2" s="52">
         <v>0.48913043478260798</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="52">
         <v>2.1739130434782601E-2</v>
       </c>
-      <c r="G2" s="56">
-        <v>0</v>
-      </c>
-      <c r="H2" s="56">
-        <v>0</v>
-      </c>
-      <c r="I2" s="56">
-        <v>0</v>
-      </c>
-      <c r="J2" s="56">
-        <v>0</v>
-      </c>
-      <c r="K2" s="56">
-        <v>0</v>
-      </c>
-      <c r="L2" s="57">
+      <c r="G2" s="52">
+        <v>0</v>
+      </c>
+      <c r="H2" s="52">
+        <v>0</v>
+      </c>
+      <c r="I2" s="52">
+        <v>0</v>
+      </c>
+      <c r="J2" s="52">
+        <v>0</v>
+      </c>
+      <c r="K2" s="52">
+        <v>0</v>
+      </c>
+      <c r="L2" s="53">
         <v>0</v>
       </c>
       <c r="M2" s="1">
@@ -2880,38 +2900,38 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="56">
+      <c r="C2" s="54"/>
+      <c r="D2" s="52">
         <v>0.15625</v>
       </c>
-      <c r="E2" s="56">
-        <v>0</v>
-      </c>
-      <c r="F2" s="56">
+      <c r="E2" s="52">
+        <v>0</v>
+      </c>
+      <c r="F2" s="52">
         <v>0.25</v>
       </c>
-      <c r="G2" s="56">
+      <c r="G2" s="52">
         <v>9.375E-2</v>
       </c>
-      <c r="H2" s="56">
-        <v>0</v>
-      </c>
-      <c r="I2" s="56">
+      <c r="H2" s="52">
+        <v>0</v>
+      </c>
+      <c r="I2" s="52">
         <v>3.125E-2</v>
       </c>
-      <c r="J2" s="56">
+      <c r="J2" s="52">
         <v>0.4375</v>
       </c>
-      <c r="K2" s="56">
-        <v>0</v>
-      </c>
-      <c r="L2" s="57">
+      <c r="K2" s="52">
+        <v>0</v>
+      </c>
+      <c r="L2" s="53">
         <v>3.125E-2</v>
       </c>
       <c r="M2" s="1">
@@ -3395,7 +3415,7 @@
       <c r="B5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="64" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="33">
@@ -3427,26 +3447,26 @@
       <c r="B6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="31">
-        <v>0</v>
-      </c>
-      <c r="E6" s="12">
-        <v>0</v>
-      </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="12">
+      <c r="D6" s="32">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="6">
         <v>0.18181818181818099</v>
       </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="12">
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="6">
         <v>0.72727272727272696</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="29"/>
       <c r="M6" s="1">
         <f t="shared" si="0"/>
         <v>0.90909090909090795</v>
@@ -3459,26 +3479,26 @@
       <c r="B7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="33">
         <v>0.125</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="3">
         <v>0.875</v>
       </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="12">
-        <v>0</v>
-      </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="12">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="25"/>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -3491,26 +3511,26 @@
       <c r="B8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <v>0.1</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="6">
         <v>0.8</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="12">
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="6">
         <v>0.1</v>
       </c>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="12">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="29"/>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -3523,7 +3543,7 @@
       <c r="B9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="66" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="31">
@@ -3555,7 +3575,7 @@
       <c r="B10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="65" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="32">
@@ -3584,10 +3604,10 @@
       <c r="A11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="55" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="12">
@@ -3614,7 +3634,7 @@
       <c r="A12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="54" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="19" t="s">
